--- a/ro_workstation/data/mis/archive/20260331.xlsx
+++ b/ro_workstation/data/mis/archive/20260331.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A5B32D-B857-46B1-87BB-E031DACAA453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -152,7 +161,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,14 +170,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1" tint="0.0499899983406067"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -198,129 +201,37 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -594,12 +505,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="19" max="19" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,7 +633,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="15">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -774,10 +689,10 @@
         <v>19.063429366000005</v>
       </c>
       <c r="S2" s="4">
-        <v>2.659219185</v>
+        <v>6.1958381999999992E-2</v>
       </c>
       <c r="T2" s="4">
-        <v>27.409764065000012</v>
+        <v>45.643704320000012</v>
       </c>
       <c r="U2" s="4">
         <v>120.28898941399999</v>
@@ -837,7 +752,7 @@
         <v>2.9941510000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -893,10 +808,10 @@
         <v>26.474263200000003</v>
       </c>
       <c r="S3" s="3">
-        <v>26.30762</v>
+        <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>37.980756900000003</v>
+        <v>116.57427499999996</v>
       </c>
       <c r="U3" s="3">
         <v>624.97881769999992</v>
@@ -929,13 +844,13 @@
         <v>22.27</v>
       </c>
       <c r="AE3" s="1">
-        <v>77.769999999999996</v>
+        <v>77.77</v>
       </c>
       <c r="AF3" s="1">
         <v>87</v>
       </c>
       <c r="AG3" s="1">
-        <v>-9.2300000000000004</v>
+        <v>-9.23</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -956,7 +871,7 @@
         <v>8.3221000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="15">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1012,10 +927,10 @@
         <v>80.472851600000013</v>
       </c>
       <c r="S4" s="3">
-        <v>0.54447690000000004</v>
+        <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>17.709442800000001</v>
+        <v>22.755375599999994</v>
       </c>
       <c r="U4" s="3">
         <v>130.17756209999999</v>
@@ -1045,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="AD4" s="1">
-        <v>21.199999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="AE4" s="1">
-        <v>37.969999999999999</v>
+        <v>37.97</v>
       </c>
       <c r="AF4" s="1">
         <v>35</v>
       </c>
       <c r="AG4" s="1">
-        <v>2.9700000000000002</v>
+        <v>2.97</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -1075,7 +990,7 @@
         <v>0.10975</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1134,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>37.067189299999995</v>
+        <v>91.354987599999959</v>
       </c>
       <c r="U5" s="3">
         <v>247.50111039999996</v>
@@ -1164,16 +1079,16 @@
         <v>0</v>
       </c>
       <c r="AD5" s="1">
-        <v>39.579999999999998</v>
+        <v>39.58</v>
       </c>
       <c r="AE5" s="1">
-        <v>70.920000000000002</v>
+        <v>70.92</v>
       </c>
       <c r="AF5" s="1">
         <v>45</v>
       </c>
       <c r="AG5" s="1">
-        <v>25.920000000000002</v>
+        <v>25.92</v>
       </c>
       <c r="AH5" s="1">
         <v>0</v>
@@ -1194,7 +1109,7 @@
         <v>7.1046199999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="15">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1250,10 +1165,10 @@
         <v>30.433004200000003</v>
       </c>
       <c r="S6" s="3">
-        <v>3.0630697999999996</v>
+        <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>53.731116</v>
+        <v>67.762505800000085</v>
       </c>
       <c r="U6" s="3">
         <v>391.27184200000016</v>
@@ -1274,7 +1189,7 @@
         <v>8633.9201909999992</v>
       </c>
       <c r="AA6" s="1">
-        <v>61.640000000000001</v>
+        <v>61.64</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -1283,16 +1198,16 @@
         <v>0</v>
       </c>
       <c r="AD6" s="1">
-        <v>26.300000000000001</v>
+        <v>26.3</v>
       </c>
       <c r="AE6" s="1">
-        <v>87.939999999999998</v>
+        <v>87.94</v>
       </c>
       <c r="AF6" s="1">
         <v>50</v>
       </c>
       <c r="AG6" s="1">
-        <v>37.939999999999998</v>
+        <v>37.94</v>
       </c>
       <c r="AH6" s="1">
         <v>0</v>
@@ -1313,7 +1228,7 @@
         <v>14.533099999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="15">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1372,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>1.5803399999999999</v>
+        <v>20.101621099999996</v>
       </c>
       <c r="U7" s="3">
         <v>155.4994524</v>
@@ -1393,7 +1308,7 @@
         <v>6366.8882773999994</v>
       </c>
       <c r="AA7" s="1">
-        <v>24.530000000000001</v>
+        <v>24.53</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
@@ -1405,13 +1320,13 @@
         <v>8.5</v>
       </c>
       <c r="AE7" s="1">
-        <v>33.030000000000001</v>
+        <v>33.03</v>
       </c>
       <c r="AF7" s="1">
         <v>45</v>
       </c>
       <c r="AG7" s="1">
-        <v>-11.970000000000001</v>
+        <v>-11.97</v>
       </c>
       <c r="AH7" s="1">
         <v>0</v>
@@ -1426,13 +1341,13 @@
         <v>0.44341999999999998</v>
       </c>
       <c r="AL7" s="1">
-        <v>0.0040299999999999997</v>
+        <v>4.0299999999999997E-3</v>
       </c>
       <c r="AM7" s="1">
         <v>5.0019</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="15">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1488,10 +1403,10 @@
         <v>56.959193600000013</v>
       </c>
       <c r="S8" s="3">
-        <v>6.1166046999999999</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>60.693583600000004</v>
+        <v>76.925927299999969</v>
       </c>
       <c r="U8" s="3">
         <v>160.68154429999998</v>
@@ -1521,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="1">
-        <v>11.369999999999999</v>
+        <v>11.37</v>
       </c>
       <c r="AE8" s="1">
         <v>30.43</v>
@@ -1530,7 +1445,7 @@
         <v>35</v>
       </c>
       <c r="AG8" s="1">
-        <v>-4.5700000000000003</v>
+        <v>-4.57</v>
       </c>
       <c r="AH8" s="1">
         <v>0</v>
@@ -1542,16 +1457,16 @@
         <v>0.91003000000000001</v>
       </c>
       <c r="AK8" s="1">
-        <v>0.030040000000000001</v>
+        <v>3.0040000000000001E-2</v>
       </c>
       <c r="AL8" s="1">
-        <v>0.070790000000000006</v>
+        <v>7.0790000000000006E-2</v>
       </c>
       <c r="AM8" s="1">
         <v>0.88414999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="15">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1610,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>255.14374639999997</v>
+        <v>303.13475840000001</v>
       </c>
       <c r="U9" s="3">
         <v>563.27298070000006</v>
@@ -1643,13 +1558,13 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="AE9" s="1">
-        <v>43.170000000000002</v>
+        <v>43.17</v>
       </c>
       <c r="AF9" s="1">
         <v>40</v>
       </c>
       <c r="AG9" s="1">
-        <v>3.1699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="AH9" s="1">
         <v>0</v>
@@ -1670,7 +1585,7 @@
         <v>2.7176</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="15">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1729,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>774.45306679999999</v>
+        <v>1553.1776100000004</v>
       </c>
       <c r="U10" s="3">
         <v>1572.9844612000004</v>
@@ -1750,16 +1665,16 @@
         <v>15346.537002700001</v>
       </c>
       <c r="AA10" s="1">
-        <v>28.420000000000002</v>
+        <v>28.42</v>
       </c>
       <c r="AB10" s="1">
-        <v>7.6100000000000003</v>
+        <v>7.61</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>40.539999999999999</v>
+        <v>40.54</v>
       </c>
       <c r="AE10" s="1">
         <v>76.569999999999993</v>
@@ -1768,7 +1683,7 @@
         <v>80</v>
       </c>
       <c r="AG10" s="1">
-        <v>-3.4300000000000002</v>
+        <v>-3.43</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1789,7 +1704,7 @@
         <v>180.05985000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="15">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1845,10 +1760,10 @@
         <v>22.022215200000002</v>
       </c>
       <c r="S11" s="3">
-        <v>0.88145810000000002</v>
+        <v>0.8814381</v>
       </c>
       <c r="T11" s="3">
-        <v>1.6354440000000001</v>
+        <v>46.851609500000052</v>
       </c>
       <c r="U11" s="3">
         <v>233.13158380000004</v>
@@ -1869,7 +1784,7 @@
         <v>10071.054588200001</v>
       </c>
       <c r="AA11" s="1">
-        <v>27.149999999999999</v>
+        <v>27.15</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1881,7 +1796,7 @@
         <v>28.18</v>
       </c>
       <c r="AE11" s="1">
-        <v>55.329999999999998</v>
+        <v>55.33</v>
       </c>
       <c r="AF11" s="1">
         <v>70</v>
@@ -1908,7 +1823,7 @@
         <v>7.3209200000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="15">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1964,10 +1879,10 @@
         <v>13.263703800000002</v>
       </c>
       <c r="S12" s="3">
-        <v>0.88345149999999995</v>
+        <v>0</v>
       </c>
       <c r="T12" s="3">
-        <v>25.985852199999997</v>
+        <v>34.44191930000008</v>
       </c>
       <c r="U12" s="3">
         <v>1162.1696104</v>
@@ -1988,7 +1903,7 @@
         <v>7811.6613082000003</v>
       </c>
       <c r="AA12" s="1">
-        <v>37.579999999999998</v>
+        <v>37.58</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
@@ -1997,16 +1912,16 @@
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>13.960000000000001</v>
+        <v>13.96</v>
       </c>
       <c r="AE12" s="1">
-        <v>51.539999999999999</v>
+        <v>51.54</v>
       </c>
       <c r="AF12" s="1">
         <v>35</v>
       </c>
       <c r="AG12" s="1">
-        <v>16.539999999999999</v>
+        <v>16.54</v>
       </c>
       <c r="AH12" s="1">
         <v>0</v>
@@ -2027,7 +1942,7 @@
         <v>0.86509999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="15">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2083,10 +1998,10 @@
         <v>22.646997200000001</v>
       </c>
       <c r="S13" s="3">
-        <v>0.70318190000000003</v>
+        <v>0.70318250000000004</v>
       </c>
       <c r="T13" s="3">
-        <v>19.518543699999999</v>
+        <v>32.150271999999987</v>
       </c>
       <c r="U13" s="3">
         <v>102.8764571</v>
@@ -2116,16 +2031,16 @@
         <v>0</v>
       </c>
       <c r="AD13" s="1">
-        <v>22.649999999999999</v>
+        <v>22.65</v>
       </c>
       <c r="AE13" s="1">
-        <v>62.420000000000002</v>
+        <v>62.42</v>
       </c>
       <c r="AF13" s="1">
         <v>30</v>
       </c>
       <c r="AG13" s="1">
-        <v>32.420000000000002</v>
+        <v>32.42</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2140,13 +2055,13 @@
         <v>6.7509399999999999</v>
       </c>
       <c r="AL13" s="1">
-        <v>0.00141</v>
+        <v>1.41E-3</v>
       </c>
       <c r="AM13" s="1">
-        <v>0.00093999999999999997</v>
+        <v>9.3999999999999997E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="15">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2205,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
-        <v>50.458103300000005</v>
+        <v>55.625059600000007</v>
       </c>
       <c r="U14" s="3">
         <v>110.44382910000002</v>
@@ -2253,19 +2168,19 @@
         <v>152.72031430000001</v>
       </c>
       <c r="AJ14" s="1">
-        <v>0.03789</v>
+        <v>3.789E-2</v>
       </c>
       <c r="AK14" s="1">
-        <v>0.00048999999999999998</v>
+        <v>4.8999999999999998E-4</v>
       </c>
       <c r="AL14" s="1">
         <v>6.8592899999999997</v>
       </c>
       <c r="AM14" s="1">
-        <v>0.00093999999999999997</v>
+        <v>9.3999999999999997E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="15">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2321,10 +2236,10 @@
         <v>79.9558751</v>
       </c>
       <c r="S15" s="3">
-        <v>39.950971200000005</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>60.721989100000009</v>
+        <v>117.1408503</v>
       </c>
       <c r="U15" s="3">
         <v>299.42328400000002</v>
@@ -2345,7 +2260,7 @@
         <v>5627.4598616000003</v>
       </c>
       <c r="AA15" s="1">
-        <v>42.729999999999997</v>
+        <v>42.73</v>
       </c>
       <c r="AB15" s="1">
         <v>0</v>
@@ -2354,16 +2269,16 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1">
-        <v>6.4800000000000004</v>
+        <v>6.48</v>
       </c>
       <c r="AE15" s="1">
-        <v>49.210000000000001</v>
+        <v>49.21</v>
       </c>
       <c r="AF15" s="1">
         <v>30</v>
       </c>
       <c r="AG15" s="1">
-        <v>19.210000000000001</v>
+        <v>19.21</v>
       </c>
       <c r="AH15" s="1">
         <v>400</v>
@@ -2384,7 +2299,7 @@
         <v>2.5365700000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="15">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2440,10 +2355,10 @@
         <v>96.699418699999995</v>
       </c>
       <c r="S16" s="3">
-        <v>2.5873030999999997</v>
+        <v>1.5839730999999999</v>
       </c>
       <c r="T16" s="3">
-        <v>32.173941999999997</v>
+        <v>53.429317600000019</v>
       </c>
       <c r="U16" s="3">
         <v>446.28531939999999</v>
@@ -2464,7 +2379,7 @@
         <v>12165.066160599999</v>
       </c>
       <c r="AA16" s="1">
-        <v>49.359999999999999</v>
+        <v>49.36</v>
       </c>
       <c r="AB16" s="1">
         <v>0</v>
@@ -2473,16 +2388,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="1">
-        <v>6.2800000000000002</v>
+        <v>6.28</v>
       </c>
       <c r="AE16" s="1">
-        <v>55.640000000000001</v>
+        <v>55.64</v>
       </c>
       <c r="AF16" s="1">
         <v>33</v>
       </c>
       <c r="AG16" s="1">
-        <v>22.640000000000001</v>
+        <v>22.64</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -2503,7 +2418,7 @@
         <v>0.65498999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="15">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2559,10 +2474,10 @@
         <v>32.051857400000003</v>
       </c>
       <c r="S17" s="3">
-        <v>7.2354799999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" s="3">
-        <v>36.998535400000002</v>
+        <v>51.466699999999996</v>
       </c>
       <c r="U17" s="3">
         <v>183.529741</v>
@@ -2595,7 +2510,7 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="AE17" s="1">
-        <v>45.119999999999997</v>
+        <v>45.12</v>
       </c>
       <c r="AF17" s="1">
         <v>35</v>
@@ -2622,7 +2537,7 @@
         <v>1.1933400000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="15">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2681,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
-        <v>6.6109898000000005</v>
+        <v>41.819518600000002</v>
       </c>
       <c r="U18" s="3">
         <v>82.836569699999998</v>
@@ -2738,10 +2653,10 @@
         <v>2.5019100000000001</v>
       </c>
       <c r="AM18" s="1">
-        <v>0.0019300000000000001</v>
+        <v>1.9300000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="15">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2797,10 +2712,10 @@
         <v>108.67307979999998</v>
       </c>
       <c r="S19" s="3">
-        <v>3.4951299999999996</v>
+        <v>0</v>
       </c>
       <c r="T19" s="3">
-        <v>51.382502200000005</v>
+        <v>100.51790629999996</v>
       </c>
       <c r="U19" s="3">
         <v>695.14612669999997</v>
@@ -2839,7 +2754,7 @@
         <v>25</v>
       </c>
       <c r="AG19" s="1">
-        <v>-22.460000000000001</v>
+        <v>-22.46</v>
       </c>
       <c r="AH19" s="1">
         <v>0</v>
@@ -2860,7 +2775,7 @@
         <v>1.1154500000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="15">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2919,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>58.697660900000002</v>
+        <v>69.075832000000005</v>
       </c>
       <c r="U20" s="3">
         <v>169.49668940000004</v>
@@ -2940,7 +2855,7 @@
         <v>7061.8403475999994</v>
       </c>
       <c r="AA20" s="1">
-        <v>45.890000000000001</v>
+        <v>45.89</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2949,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>10.449999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="AE20" s="1">
-        <v>56.340000000000003</v>
+        <v>56.34</v>
       </c>
       <c r="AF20" s="1">
         <v>30</v>
@@ -2979,7 +2894,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="15">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3038,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="3">
-        <v>56.630049499999991</v>
+        <v>60.619488500000003</v>
       </c>
       <c r="U21" s="3">
         <v>192.08799720000002</v>
@@ -3071,13 +2986,13 @@
         <v>13.6</v>
       </c>
       <c r="AE21" s="1">
-        <v>26.829999999999998</v>
+        <v>26.83</v>
       </c>
       <c r="AF21" s="1">
         <v>30</v>
       </c>
       <c r="AG21" s="1">
-        <v>-3.1699999999999999</v>
+        <v>-3.17</v>
       </c>
       <c r="AH21" s="1">
         <v>0</v>
@@ -3092,13 +3007,13 @@
         <v>0.33148</v>
       </c>
       <c r="AL21" s="1">
-        <v>0.066379999999999995</v>
+        <v>6.6379999999999995E-2</v>
       </c>
       <c r="AM21" s="1">
-        <v>0.028320000000000001</v>
+        <v>2.8320000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="15">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3154,10 +3069,10 @@
         <v>54.903941999999994</v>
       </c>
       <c r="S22" s="3">
-        <v>8.6873097000000001</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>41.778671600000003</v>
+        <v>71.555516599999976</v>
       </c>
       <c r="U22" s="3">
         <v>186.31200489999998</v>
@@ -3178,7 +3093,7 @@
         <v>5578.4743435999999</v>
       </c>
       <c r="AA22" s="1">
-        <v>48.890000000000001</v>
+        <v>48.89</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3187,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>35.859999999999999</v>
+        <v>35.86</v>
       </c>
       <c r="AE22" s="1">
         <v>84.75</v>
@@ -3205,7 +3120,7 @@
         <v>214.1566564</v>
       </c>
       <c r="AJ22" s="1">
-        <v>0.027089999999999999</v>
+        <v>2.7089999999999999E-2</v>
       </c>
       <c r="AK22" s="1">
         <v>0.39182</v>
@@ -3217,7 +3132,7 @@
         <v>0.28193000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="15">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3273,10 +3188,10 @@
         <v>6.3396493999999999</v>
       </c>
       <c r="S23" s="3">
-        <v>1.2203168</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>22.532133999999999</v>
+        <v>51.461922399999999</v>
       </c>
       <c r="U23" s="3">
         <v>98.410133600000009</v>
@@ -3306,10 +3221,10 @@
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>82.239999999999995</v>
+        <v>82.24</v>
       </c>
       <c r="AE23" s="1">
-        <v>141.46000000000001</v>
+        <v>141.46</v>
       </c>
       <c r="AF23" s="1">
         <v>70</v>
@@ -3336,7 +3251,7 @@
         <v>4.7040499999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="15">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3392,10 +3307,10 @@
         <v>12.7234926</v>
       </c>
       <c r="S24" s="3">
-        <v>12.2823227</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>10.334869000000001</v>
+        <v>36.214007799999976</v>
       </c>
       <c r="U24" s="3">
         <v>156.34511119999999</v>
@@ -3416,7 +3331,7 @@
         <v>5025.3509590999993</v>
       </c>
       <c r="AA24" s="1">
-        <v>21.079999999999998</v>
+        <v>21.08</v>
       </c>
       <c r="AB24" s="1">
         <v>12.25</v>
@@ -3428,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="AE24" s="1">
-        <v>33.329999999999998</v>
+        <v>33.33</v>
       </c>
       <c r="AF24" s="1">
         <v>45</v>
@@ -3455,7 +3370,7 @@
         <v>11.32147</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="15">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3514,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="3">
-        <v>28.050366199999999</v>
+        <v>28.776675200000007</v>
       </c>
       <c r="U25" s="3">
         <v>40.06970290000001</v>
@@ -3535,7 +3450,7 @@
         <v>3234.8239198000001</v>
       </c>
       <c r="AA25" s="1">
-        <v>21.379999999999999</v>
+        <v>21.38</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -3553,7 +3468,7 @@
         <v>25</v>
       </c>
       <c r="AG25" s="1">
-        <v>6.5700000000000003</v>
+        <v>6.57</v>
       </c>
       <c r="AH25" s="1">
         <v>0</v>
@@ -3574,7 +3489,7 @@
         <v>0.49512</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="15">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3630,10 +3545,10 @@
         <v>20.636569099999999</v>
       </c>
       <c r="S26" s="3">
-        <v>4.6584000000000003</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>15.366605</v>
+        <v>45.425004999999992</v>
       </c>
       <c r="U26" s="3">
         <v>83.744878299999996</v>
@@ -3666,13 +3581,13 @@
         <v>11.9</v>
       </c>
       <c r="AE26" s="1">
-        <v>23.890000000000001</v>
+        <v>23.89</v>
       </c>
       <c r="AF26" s="1">
         <v>32</v>
       </c>
       <c r="AG26" s="1">
-        <v>-8.1099999999999994</v>
+        <v>-8.11</v>
       </c>
       <c r="AH26" s="1">
         <v>0</v>
@@ -3684,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="1">
-        <v>0.90000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="AL26" s="1">
         <v>1.96305</v>
@@ -3693,7 +3608,7 @@
         <v>3.6840700000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="15">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3752,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>75.63719500000002</v>
+        <v>92.647845000000018</v>
       </c>
       <c r="U27" s="3">
         <v>155.7384654</v>
@@ -3773,7 +3688,7 @@
         <v>7851.2096683999998</v>
       </c>
       <c r="AA27" s="1">
-        <v>41.159999999999997</v>
+        <v>41.16</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -3785,13 +3700,13 @@
         <v>38.450000000000003</v>
       </c>
       <c r="AE27" s="1">
-        <v>79.609999999999999</v>
+        <v>79.61</v>
       </c>
       <c r="AF27" s="1">
         <v>36</v>
       </c>
       <c r="AG27" s="1">
-        <v>43.609999999999999</v>
+        <v>43.61</v>
       </c>
       <c r="AH27" s="1">
         <v>0</v>
@@ -3812,7 +3727,7 @@
         <v>7.5196399999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="15">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3868,10 +3783,10 @@
         <v>31.828303699999999</v>
       </c>
       <c r="S28" s="3">
-        <v>7.9416051999999997</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3">
-        <v>18.735258599999998</v>
+        <v>35.896037799999995</v>
       </c>
       <c r="U28" s="3">
         <v>253.851169</v>
@@ -3901,16 +3816,16 @@
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>2.6899999999999999</v>
+        <v>2.69</v>
       </c>
       <c r="AE28" s="1">
-        <v>22.940000000000001</v>
+        <v>22.94</v>
       </c>
       <c r="AF28" s="1">
         <v>30</v>
       </c>
       <c r="AG28" s="1">
-        <v>-7.0599999999999996</v>
+        <v>-7.06</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -3931,7 +3846,7 @@
         <v>5.9265600000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="15">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3990,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>7.9670945999999994</v>
+        <v>18.749436599999992</v>
       </c>
       <c r="U29" s="3">
         <v>108.3316097</v>
@@ -4020,16 +3935,16 @@
         <v>0</v>
       </c>
       <c r="AD29" s="1">
-        <v>8.4100000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="AE29" s="1">
-        <v>45.299999999999997</v>
+        <v>45.3</v>
       </c>
       <c r="AF29" s="1">
         <v>40</v>
       </c>
       <c r="AG29" s="1">
-        <v>5.2999999999999998</v>
+        <v>5.3</v>
       </c>
       <c r="AH29" s="1">
         <v>0</v>
@@ -4038,7 +3953,7 @@
         <v>343.86590719999998</v>
       </c>
       <c r="AJ29" s="1">
-        <v>0.054760000000000003</v>
+        <v>5.4760000000000003E-2</v>
       </c>
       <c r="AK29" s="1">
         <v>1.2500199999999999</v>
@@ -4050,7 +3965,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="15">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4109,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <v>16.450920700000001</v>
+        <v>18.307706500000005</v>
       </c>
       <c r="U30" s="3">
         <v>81.687984400000005</v>
@@ -4130,10 +4045,10 @@
         <v>9296.3004184000001</v>
       </c>
       <c r="AA30" s="1">
-        <v>25.440000000000001</v>
+        <v>25.44</v>
       </c>
       <c r="AB30" s="1">
-        <v>11.029999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
@@ -4142,13 +4057,13 @@
         <v>0</v>
       </c>
       <c r="AE30" s="1">
-        <v>36.469999999999999</v>
+        <v>36.47</v>
       </c>
       <c r="AF30" s="1">
         <v>40</v>
       </c>
       <c r="AG30" s="1">
-        <v>-3.5299999999999998</v>
+        <v>-3.53</v>
       </c>
       <c r="AH30" s="1">
         <v>0</v>
@@ -4157,7 +4072,7 @@
         <v>376.34160070000001</v>
       </c>
       <c r="AJ30" s="1">
-        <v>2.0000000000000002E-05</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="AK30" s="1">
         <v>3.0000200000000001</v>
@@ -4169,7 +4084,7 @@
         <v>2.7058</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="15">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4228,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <v>28.519532800000004</v>
+        <v>66.832942299999999</v>
       </c>
       <c r="U31" s="3">
         <v>129.5509199</v>
@@ -4261,13 +4176,13 @@
         <v>18.68</v>
       </c>
       <c r="AE31" s="1">
-        <v>52.609999999999999</v>
+        <v>52.61</v>
       </c>
       <c r="AF31" s="1">
         <v>30</v>
       </c>
       <c r="AG31" s="1">
-        <v>22.609999999999999</v>
+        <v>22.61</v>
       </c>
       <c r="AH31" s="1">
         <v>0</v>
@@ -4288,7 +4203,7 @@
         <v>3.2392400000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="15">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4344,10 +4259,10 @@
         <v>26.817837900000001</v>
       </c>
       <c r="S32" s="3">
-        <v>0.77999999999999992</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>5.2609428999999999</v>
+        <v>15.880366500000004</v>
       </c>
       <c r="U32" s="3">
         <v>98.628184000000005</v>
@@ -4407,7 +4322,7 @@
         <v>0.96345000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="15">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4463,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>21.200000799999998</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>35.211992500000001</v>
+        <v>112.7763442</v>
       </c>
       <c r="U33" s="3">
         <v>112.7763442</v>
@@ -4505,7 +4420,7 @@
         <v>43</v>
       </c>
       <c r="AG33" s="1">
-        <v>-1.4299999999999999</v>
+        <v>-1.43</v>
       </c>
       <c r="AH33" s="1">
         <v>0</v>
@@ -4514,19 +4429,19 @@
         <v>394.3496864</v>
       </c>
       <c r="AJ33" s="1">
-        <v>0.0015399999999999999</v>
+        <v>1.5399999999999999E-3</v>
       </c>
       <c r="AK33" s="1">
-        <v>0.030949999999999998</v>
+        <v>3.0949999999999998E-2</v>
       </c>
       <c r="AL33" s="1">
         <v>1.37096</v>
       </c>
       <c r="AM33" s="1">
-        <v>0.00025000000000000001</v>
+        <v>2.5000000000000001E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="15">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4582,10 +4497,10 @@
         <v>25.946819999999999</v>
       </c>
       <c r="S34" s="3">
-        <v>8.4208599999999993</v>
+        <v>0</v>
       </c>
       <c r="T34" s="3">
-        <v>44.296720699999995</v>
+        <v>69.80052809999998</v>
       </c>
       <c r="U34" s="3">
         <v>109.45489789999998</v>
@@ -4606,10 +4521,10 @@
         <v>8769.8551050000005</v>
       </c>
       <c r="AA34" s="1">
-        <v>33.609999999999999</v>
+        <v>33.61</v>
       </c>
       <c r="AB34" s="1">
-        <v>9.0700000000000003</v>
+        <v>9.07</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -4618,13 +4533,13 @@
         <v>46.18</v>
       </c>
       <c r="AE34" s="1">
-        <v>88.859999999999999</v>
+        <v>88.86</v>
       </c>
       <c r="AF34" s="1">
         <v>55</v>
       </c>
       <c r="AG34" s="1">
-        <v>33.859999999999999</v>
+        <v>33.86</v>
       </c>
       <c r="AH34" s="1">
         <v>0</v>
@@ -4642,10 +4557,10 @@
         <v>1.8021799999999999</v>
       </c>
       <c r="AM34" s="1">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:39" ht="15">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4698,13 +4613,13 @@
         <v>291.77402190000004</v>
       </c>
       <c r="R35" s="3">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="S35" s="3">
-        <v>0.96666669999999999</v>
+        <v>0.91666669999999995</v>
       </c>
       <c r="T35" s="3">
-        <v>11.838640699999999</v>
+        <v>13.503552599999933</v>
       </c>
       <c r="U35" s="3">
         <v>309.34424119999994</v>
@@ -4725,7 +4640,7 @@
         <v>7022.7325234999998</v>
       </c>
       <c r="AA35" s="1">
-        <v>6.5800000000000001</v>
+        <v>6.58</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -4764,7 +4679,7 @@
         <v>1.05585</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="15">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4823,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="3">
-        <v>47.4411269</v>
+        <v>47.501431000000004</v>
       </c>
       <c r="U36" s="3">
         <v>189.00294689999998</v>
@@ -4856,13 +4771,13 @@
         <v>15.6</v>
       </c>
       <c r="AE36" s="1">
-        <v>52.049999999999997</v>
+        <v>52.05</v>
       </c>
       <c r="AF36" s="1">
         <v>33</v>
       </c>
       <c r="AG36" s="1">
-        <v>19.050000000000001</v>
+        <v>19.05</v>
       </c>
       <c r="AH36" s="1">
         <v>0</v>
@@ -4880,10 +4795,10 @@
         <v>3.8515600000000001</v>
       </c>
       <c r="AM36" s="1">
-        <v>0.059749999999999998</v>
+        <v>5.9749999999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="15">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4942,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="3">
-        <v>83.969880499999988</v>
+        <v>89.086568799999995</v>
       </c>
       <c r="U37" s="3">
         <v>112.67100359999999</v>
@@ -4963,7 +4878,7 @@
         <v>10764.5485646</v>
       </c>
       <c r="AA37" s="1">
-        <v>20.210000000000001</v>
+        <v>20.21</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
@@ -4975,13 +4890,13 @@
         <v>11.94</v>
       </c>
       <c r="AE37" s="1">
-        <v>32.149999999999999</v>
+        <v>32.15</v>
       </c>
       <c r="AF37" s="1">
         <v>34</v>
       </c>
       <c r="AG37" s="1">
-        <v>-1.8500000000000001</v>
+        <v>-1.85</v>
       </c>
       <c r="AH37" s="1">
         <v>0</v>
@@ -4990,19 +4905,19 @@
         <v>390.33103770000002</v>
       </c>
       <c r="AJ37" s="1">
-        <v>0.060630000000000003</v>
+        <v>6.0630000000000003E-2</v>
       </c>
       <c r="AK37" s="1">
         <v>0.15558</v>
       </c>
       <c r="AL37" s="1">
-        <v>0.075550000000000006</v>
+        <v>7.5550000000000006E-2</v>
       </c>
       <c r="AM37" s="1">
-        <v>0.022720000000000001</v>
+        <v>2.2720000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="15">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5058,10 +4973,10 @@
         <v>19.0973206</v>
       </c>
       <c r="S38" s="3">
-        <v>2.4679017999999999</v>
+        <v>0</v>
       </c>
       <c r="T38" s="3">
-        <v>21.173886500000002</v>
+        <v>33.6908083</v>
       </c>
       <c r="U38" s="3">
         <v>99.488479400000003</v>
@@ -5082,7 +4997,7 @@
         <v>7153.1224789000007</v>
       </c>
       <c r="AA38" s="1">
-        <v>22.149999999999999</v>
+        <v>22.15</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
@@ -5091,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="AD38" s="1">
-        <v>32.439999999999998</v>
+        <v>32.44</v>
       </c>
       <c r="AE38" s="1">
-        <v>54.590000000000003</v>
+        <v>54.59</v>
       </c>
       <c r="AF38" s="1">
         <v>34</v>
@@ -5109,7 +5024,7 @@
         <v>287.5915038</v>
       </c>
       <c r="AJ38" s="1">
-        <v>0.013440000000000001</v>
+        <v>1.3440000000000001E-2</v>
       </c>
       <c r="AK38" s="1">
         <v>23.326619999999998</v>
@@ -5118,10 +5033,10 @@
         <v>15.10314</v>
       </c>
       <c r="AM38" s="1">
-        <v>0.00297</v>
+        <v>2.97E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="15">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5177,10 +5092,10 @@
         <v>30.057402200000006</v>
       </c>
       <c r="S39" s="3">
-        <v>4.1133363999999997</v>
+        <v>0</v>
       </c>
       <c r="T39" s="3">
-        <v>14.764070599999995</v>
+        <v>28.338299300000013</v>
       </c>
       <c r="U39" s="3">
         <v>341.2846763</v>
@@ -5201,7 +5116,7 @@
         <v>12579.2313041</v>
       </c>
       <c r="AA39" s="1">
-        <v>22.649999999999999</v>
+        <v>22.65</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -5210,16 +5125,16 @@
         <v>0</v>
       </c>
       <c r="AD39" s="1">
-        <v>44.299999999999997</v>
+        <v>44.3</v>
       </c>
       <c r="AE39" s="1">
-        <v>66.950000000000003</v>
+        <v>66.95</v>
       </c>
       <c r="AF39" s="1">
         <v>38</v>
       </c>
       <c r="AG39" s="1">
-        <v>28.949999999999999</v>
+        <v>28.95</v>
       </c>
       <c r="AH39" s="1">
         <v>0</v>
@@ -5228,19 +5143,19 @@
         <v>544.11298729999999</v>
       </c>
       <c r="AJ39" s="1">
-        <v>0.00038000000000000002</v>
+        <v>3.8000000000000002E-4</v>
       </c>
       <c r="AK39" s="1">
-        <v>0.035040000000000002</v>
+        <v>3.5040000000000002E-2</v>
       </c>
       <c r="AL39" s="1">
-        <v>0.00096000000000000002</v>
+        <v>9.6000000000000002E-4</v>
       </c>
       <c r="AM39" s="1">
-        <v>0.042009999999999999</v>
+        <v>4.2009999999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="15">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5293,13 +5208,13 @@
         <v>35.648727299999997</v>
       </c>
       <c r="R40" s="3">
-        <v>0.32000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="S40" s="3">
-        <v>4.2579728000000001</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3">
-        <v>0.9811202</v>
+        <v>15.139092999999995</v>
       </c>
       <c r="U40" s="3">
         <v>51.107820299999993</v>
@@ -5320,7 +5235,7 @@
         <v>8719.3167412999992</v>
       </c>
       <c r="AA40" s="1">
-        <v>25.440000000000001</v>
+        <v>25.44</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -5332,7 +5247,7 @@
         <v>20.41</v>
       </c>
       <c r="AE40" s="1">
-        <v>45.850000000000001</v>
+        <v>45.85</v>
       </c>
       <c r="AF40" s="1">
         <v>35</v>
@@ -5359,7 +5274,7 @@
         <v>1.44652</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="15">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5415,10 +5330,10 @@
         <v>1.4689957</v>
       </c>
       <c r="S41" s="3">
-        <v>6.4474114999999994</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
-        <v>78.890052000000011</v>
+        <v>85.337463500000013</v>
       </c>
       <c r="U41" s="3">
         <v>86.806459200000006</v>
@@ -5439,7 +5354,7 @@
         <v>4635.5096014999999</v>
       </c>
       <c r="AA41" s="1">
-        <v>44.840000000000003</v>
+        <v>44.84</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
@@ -5448,16 +5363,16 @@
         <v>0</v>
       </c>
       <c r="AD41" s="1">
-        <v>13.029999999999999</v>
+        <v>13.03</v>
       </c>
       <c r="AE41" s="1">
-        <v>57.869999999999997</v>
+        <v>57.87</v>
       </c>
       <c r="AF41" s="1">
         <v>33</v>
       </c>
       <c r="AG41" s="1">
-        <v>24.870000000000001</v>
+        <v>24.87</v>
       </c>
       <c r="AH41" s="1">
         <v>0</v>
@@ -5469,7 +5384,7 @@
         <v>23.397929999999999</v>
       </c>
       <c r="AK41" s="1">
-        <v>0.032009999999999997</v>
+        <v>3.2009999999999997E-2</v>
       </c>
       <c r="AL41" s="1">
         <v>0.72116999999999998</v>
@@ -5478,7 +5393,7 @@
         <v>4.1247999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:39" ht="15">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5537,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>30.341504799999996</v>
+        <v>30.341504799999992</v>
       </c>
       <c r="U42" s="3">
         <v>65.914084399999993</v>
@@ -5570,13 +5485,13 @@
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>82.219999999999999</v>
+        <v>82.22</v>
       </c>
       <c r="AF42" s="1">
         <v>34</v>
       </c>
       <c r="AG42" s="1">
-        <v>48.219999999999999</v>
+        <v>48.22</v>
       </c>
       <c r="AH42" s="1">
         <v>0</v>
@@ -5588,16 +5503,16 @@
         <v>0.10518</v>
       </c>
       <c r="AK42" s="1">
-        <v>4.0000000000000003E-05</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="AL42" s="1">
-        <v>0.020389999999999998</v>
+        <v>2.0389999999999998E-2</v>
       </c>
       <c r="AM42" s="1">
         <v>0.27528000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:39" ht="15">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5653,10 +5568,10 @@
         <v>27.940264199999998</v>
       </c>
       <c r="S43" s="3">
-        <v>3.0390899999999998</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>3.8617269000000003</v>
+        <v>7.5383593000000024</v>
       </c>
       <c r="U43" s="3">
         <v>35.478623499999998</v>
@@ -5677,7 +5592,7 @@
         <v>11115.6827514</v>
       </c>
       <c r="AA43" s="1">
-        <v>141.40000000000001</v>
+        <v>141.4</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
@@ -5689,13 +5604,13 @@
         <v>15.84</v>
       </c>
       <c r="AE43" s="1">
-        <v>157.24000000000001</v>
+        <v>157.24</v>
       </c>
       <c r="AF43" s="1">
         <v>30</v>
       </c>
       <c r="AG43" s="1">
-        <v>127.23999999999999</v>
+        <v>127.24</v>
       </c>
       <c r="AH43" s="1">
         <v>0</v>
@@ -5704,19 +5619,19 @@
         <v>379.05141070000002</v>
       </c>
       <c r="AJ43" s="1">
-        <v>1.0000000000000001E-05</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AK43" s="1">
-        <v>3.0000000000000001E-05</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="AL43" s="1">
         <v>0</v>
       </c>
       <c r="AM43" s="1">
-        <v>0.019859999999999999</v>
+        <v>1.9859999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:39" ht="15">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5775,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>21.502946600000001</v>
+        <v>22.282612499999995</v>
       </c>
       <c r="U44" s="3">
         <v>102.4998629</v>
@@ -5796,7 +5711,7 @@
         <v>4393.3398811000006</v>
       </c>
       <c r="AA44" s="1">
-        <v>24.359999999999999</v>
+        <v>24.36</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
@@ -5805,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="1">
-        <v>5.9800000000000004</v>
+        <v>5.98</v>
       </c>
       <c r="AE44" s="1">
         <v>30.34</v>
@@ -5814,7 +5729,7 @@
         <v>25</v>
       </c>
       <c r="AG44" s="1">
-        <v>5.3399999999999999</v>
+        <v>5.34</v>
       </c>
       <c r="AH44" s="1">
         <v>0</v>
@@ -5823,19 +5738,19 @@
         <v>156.19951850000001</v>
       </c>
       <c r="AJ44" s="1">
-        <v>0.032250000000000001</v>
+        <v>3.2250000000000001E-2</v>
       </c>
       <c r="AK44" s="1">
-        <v>0.021149999999999999</v>
+        <v>2.1149999999999999E-2</v>
       </c>
       <c r="AL44" s="1">
-        <v>0.090800000000000006</v>
+        <v>9.0800000000000006E-2</v>
       </c>
       <c r="AM44" s="1">
-        <v>0.072139999999999996</v>
+        <v>7.2139999999999996E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:39" ht="15">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5891,10 +5806,10 @@
         <v>24.866661300000001</v>
       </c>
       <c r="S45" s="3">
-        <v>5.6572772999999996</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>53.96880190000001</v>
+        <v>59.6260792</v>
       </c>
       <c r="U45" s="3">
         <v>109.9236324</v>
@@ -5915,7 +5830,7 @@
         <v>9673.8367088999985</v>
       </c>
       <c r="AA45" s="1">
-        <v>18.219999999999999</v>
+        <v>18.22</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
@@ -5924,16 +5839,16 @@
         <v>0</v>
       </c>
       <c r="AD45" s="1">
-        <v>39.240000000000002</v>
+        <v>39.24</v>
       </c>
       <c r="AE45" s="1">
-        <v>57.460000000000001</v>
+        <v>57.46</v>
       </c>
       <c r="AF45" s="1">
         <v>40</v>
       </c>
       <c r="AG45" s="1">
-        <v>17.460000000000001</v>
+        <v>17.46</v>
       </c>
       <c r="AH45" s="1">
         <v>0</v>
@@ -5945,16 +5860,16 @@
         <v>2.9007900000000002</v>
       </c>
       <c r="AK45" s="1">
-        <v>0.016910000000000001</v>
+        <v>1.6910000000000001E-2</v>
       </c>
       <c r="AL45" s="1">
-        <v>0.00093999999999999997</v>
+        <v>9.3999999999999997E-4</v>
       </c>
       <c r="AM45" s="1">
         <v>2.15652</v>
       </c>
     </row>
-    <row r="46" spans="1:39" ht="15">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -6010,10 +5925,10 @@
         <v>41.291792700000002</v>
       </c>
       <c r="S46" s="3">
-        <v>2.8152561</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3">
-        <v>37.994281800000003</v>
+        <v>42.009537900000005</v>
       </c>
       <c r="U46" s="3">
         <v>95.747072200000005</v>
@@ -6034,7 +5949,7 @@
         <v>6092.8181897000004</v>
       </c>
       <c r="AA46" s="1">
-        <v>34.469999999999999</v>
+        <v>34.47</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
@@ -6046,7 +5961,7 @@
         <v>14.09</v>
       </c>
       <c r="AE46" s="1">
-        <v>48.560000000000002</v>
+        <v>48.56</v>
       </c>
       <c r="AF46" s="1">
         <v>33</v>
@@ -6070,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="AM46" s="1">
-        <v>0.94999999999999996</v>
+        <v>0.95</v>
       </c>
     </row>
-    <row r="47" spans="1:39" ht="15">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6132,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
-        <v>43.240155300000005</v>
+        <v>43.240155299999977</v>
       </c>
       <c r="U47" s="3">
         <v>202.08384649999996</v>
@@ -6153,7 +6068,7 @@
         <v>8477.5324937999994</v>
       </c>
       <c r="AA47" s="1">
-        <v>28.370000000000001</v>
+        <v>28.37</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
@@ -6162,16 +6077,16 @@
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <v>22.579999999999998</v>
+        <v>22.58</v>
       </c>
       <c r="AE47" s="1">
-        <v>50.950000000000003</v>
+        <v>50.95</v>
       </c>
       <c r="AF47" s="1">
         <v>35</v>
       </c>
       <c r="AG47" s="1">
-        <v>15.949999999999999</v>
+        <v>15.95</v>
       </c>
       <c r="AH47" s="1">
         <v>0</v>
@@ -6183,16 +6098,16 @@
         <v>0.23404</v>
       </c>
       <c r="AK47" s="1">
-        <v>0.050029999999999998</v>
+        <v>5.0029999999999998E-2</v>
       </c>
       <c r="AL47" s="1">
-        <v>2.0000000000000002E-05</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="AM47" s="1">
         <v>0.10032000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:39" ht="15">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6245,7 +6160,7 @@
         <v>30.339821999999998</v>
       </c>
       <c r="R48" s="3">
-        <v>6.4699999999999998</v>
+        <v>6.47</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -6272,7 +6187,7 @@
         <v>7936.1799438000007</v>
       </c>
       <c r="AA48" s="1">
-        <v>27.719999999999999</v>
+        <v>27.72</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -6284,7 +6199,7 @@
         <v>16.18</v>
       </c>
       <c r="AE48" s="1">
-        <v>43.899999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="AF48" s="1">
         <v>27</v>
@@ -6311,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:39" ht="15">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6370,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="3">
-        <v>12.863634400000002</v>
+        <v>72.673634400000012</v>
       </c>
       <c r="U49" s="3">
         <v>133.96657240000002</v>
@@ -6400,16 +6315,16 @@
         <v>0</v>
       </c>
       <c r="AD49" s="1">
-        <v>8.1400000000000006</v>
+        <v>8.14</v>
       </c>
       <c r="AE49" s="1">
-        <v>24.239999999999998</v>
+        <v>24.24</v>
       </c>
       <c r="AF49" s="1">
         <v>27</v>
       </c>
       <c r="AG49" s="1">
-        <v>-2.7599999999999998</v>
+        <v>-2.76</v>
       </c>
       <c r="AH49" s="1">
         <v>0</v>
@@ -6418,19 +6333,19 @@
         <v>170.98306170000001</v>
       </c>
       <c r="AJ49" s="1">
-        <v>0.00012</v>
+        <v>1.2E-4</v>
       </c>
       <c r="AK49" s="1">
         <v>2.11938</v>
       </c>
       <c r="AL49" s="1">
-        <v>0.090499999999999997</v>
+        <v>9.0499999999999997E-2</v>
       </c>
       <c r="AM49" s="1">
-        <v>0.00051000000000000004</v>
+        <v>5.1000000000000004E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:39" ht="15">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6486,10 +6401,10 @@
         <v>9.5622320999999992</v>
       </c>
       <c r="S50" s="3">
-        <v>1.7046772000000001</v>
+        <v>0</v>
       </c>
       <c r="T50" s="3">
-        <v>31.558213799999997</v>
+        <v>33.262890999999996</v>
       </c>
       <c r="U50" s="3">
         <v>44.411006399999998</v>
@@ -6510,7 +6425,7 @@
         <v>3151.7232076999999</v>
       </c>
       <c r="AA50" s="1">
-        <v>5.5800000000000001</v>
+        <v>5.58</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
@@ -6519,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="AD50" s="1">
-        <v>4.7599999999999998</v>
+        <v>4.76</v>
       </c>
       <c r="AE50" s="1">
         <v>10.34</v>
@@ -6528,7 +6443,7 @@
         <v>15</v>
       </c>
       <c r="AG50" s="1">
-        <v>-4.6600000000000001</v>
+        <v>-4.66</v>
       </c>
       <c r="AH50" s="1">
         <v>0</v>
@@ -6537,7 +6452,7 @@
         <v>89.4519272</v>
       </c>
       <c r="AJ50" s="1">
-        <v>1.0000000000000001E-05</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AK50" s="1">
         <v>1.70001</v>
@@ -6549,7 +6464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" ht="15">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6605,10 +6520,10 @@
         <v>31.9726897</v>
       </c>
       <c r="S51" s="3">
-        <v>1.3322209</v>
+        <v>0</v>
       </c>
       <c r="T51" s="3">
-        <v>28.7943663</v>
+        <v>30.12658720000001</v>
       </c>
       <c r="U51" s="3">
         <v>62.099276900000014</v>
@@ -6629,7 +6544,7 @@
         <v>4863.2046416000003</v>
       </c>
       <c r="AA51" s="1">
-        <v>42.369999999999997</v>
+        <v>42.37</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
@@ -6641,13 +6556,13 @@
         <v>10.01</v>
       </c>
       <c r="AE51" s="1">
-        <v>52.380000000000003</v>
+        <v>52.38</v>
       </c>
       <c r="AF51" s="1">
         <v>25</v>
       </c>
       <c r="AG51" s="1">
-        <v>27.379999999999999</v>
+        <v>27.38</v>
       </c>
       <c r="AH51" s="1">
         <v>0</v>
@@ -6656,10 +6571,10 @@
         <v>117.6216537</v>
       </c>
       <c r="AJ51" s="1">
-        <v>0.041880000000000001</v>
+        <v>4.1880000000000001E-2</v>
       </c>
       <c r="AK51" s="1">
-        <v>0.020119999999999999</v>
+        <v>2.0119999999999999E-2</v>
       </c>
       <c r="AL51" s="1">
         <v>0.80044000000000004</v>
@@ -6668,7 +6583,7 @@
         <v>2.0729299999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:39" ht="15">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6724,10 +6639,10 @@
         <v>3.3855400000000002</v>
       </c>
       <c r="S52" s="3">
-        <v>7.4835861000000001</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>0.67264999999999997</v>
+        <v>20.341236100000003</v>
       </c>
       <c r="U52" s="3">
         <v>23.726776100000002</v>
@@ -6748,7 +6663,7 @@
         <v>2933.4732304999998</v>
       </c>
       <c r="AA52" s="1">
-        <v>59.659999999999997</v>
+        <v>59.66</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -6757,16 +6672,16 @@
         <v>0</v>
       </c>
       <c r="AD52" s="1">
-        <v>31.629999999999999</v>
+        <v>31.63</v>
       </c>
       <c r="AE52" s="1">
-        <v>91.290000000000006</v>
+        <v>91.29</v>
       </c>
       <c r="AF52" s="1">
         <v>40</v>
       </c>
       <c r="AG52" s="1">
-        <v>51.289999999999999</v>
+        <v>51.29</v>
       </c>
       <c r="AH52" s="1">
         <v>0</v>
@@ -6787,7 +6702,7 @@
         <v>3.8749199999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:39" ht="15">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6843,10 +6758,10 @@
         <v>56.335475300000006</v>
       </c>
       <c r="S53" s="3">
-        <v>35.152592399999996</v>
+        <v>2.1105777999999997</v>
       </c>
       <c r="T53" s="3">
-        <v>100.32130789999999</v>
+        <v>133.32130789999999</v>
       </c>
       <c r="U53" s="3">
         <v>283.2983107</v>
@@ -6867,7 +6782,7 @@
         <v>6402.8617396</v>
       </c>
       <c r="AA53" s="1">
-        <v>26.890000000000001</v>
+        <v>26.89</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
@@ -6876,10 +6791,10 @@
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <v>19.030000000000001</v>
+        <v>19.03</v>
       </c>
       <c r="AE53" s="1">
-        <v>45.920000000000002</v>
+        <v>45.92</v>
       </c>
       <c r="AF53" s="1">
         <v>28</v>
@@ -6906,7 +6821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="15">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6962,10 +6877,10 @@
         <v>65.504669699999994</v>
       </c>
       <c r="S54" s="3">
-        <v>33.524366900000004</v>
+        <v>0</v>
       </c>
       <c r="T54" s="3">
-        <v>54.147096100000006</v>
+        <v>101.42638220000003</v>
       </c>
       <c r="U54" s="3">
         <v>198.28555000000003</v>
@@ -7004,7 +6919,7 @@
         <v>23</v>
       </c>
       <c r="AG54" s="1">
-        <v>-5.7699999999999996</v>
+        <v>-5.77</v>
       </c>
       <c r="AH54" s="1">
         <v>0</v>
@@ -7019,13 +6934,13 @@
         <v>0.54149999999999998</v>
       </c>
       <c r="AL54" s="1">
-        <v>0.06053</v>
+        <v>6.053E-2</v>
       </c>
       <c r="AM54" s="1">
         <v>5.2675999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:39" ht="15">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7084,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="3">
-        <v>57.671018400000008</v>
+        <v>60.668291800000084</v>
       </c>
       <c r="U55" s="3">
         <v>286.16772670000006</v>
@@ -7123,7 +7038,7 @@
         <v>23</v>
       </c>
       <c r="AG55" s="1">
-        <v>41.240000000000002</v>
+        <v>41.24</v>
       </c>
       <c r="AH55" s="1">
         <v>0</v>
@@ -7132,10 +7047,10 @@
         <v>181.5544897</v>
       </c>
       <c r="AJ55" s="1">
-        <v>0.081159999999999996</v>
+        <v>8.1159999999999996E-2</v>
       </c>
       <c r="AK55" s="1">
-        <v>0.00048000000000000001</v>
+        <v>4.8000000000000001E-4</v>
       </c>
       <c r="AL55" s="1">
         <v>1.15245</v>
@@ -7144,7 +7059,7 @@
         <v>2.05585</v>
       </c>
     </row>
-    <row r="56" spans="1:39" ht="15">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7161,7 +7076,7 @@
         <v>919.21199319999994</v>
       </c>
       <c r="F56" s="3">
-        <v>49.520000000000003</v>
+        <v>49.52</v>
       </c>
       <c r="G56" s="3">
         <v>968.73199319999992</v>
@@ -7197,13 +7112,13 @@
         <v>0</v>
       </c>
       <c r="R56" s="3">
-        <v>4.4199999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="S56" s="3">
         <v>0</v>
       </c>
       <c r="T56" s="3">
-        <v>0.86177000000000004</v>
+        <v>0.86176999999999992</v>
       </c>
       <c r="U56" s="3">
         <v>5.2817699999999999</v>
@@ -7233,16 +7148,16 @@
         <v>0</v>
       </c>
       <c r="AD56" s="1">
-        <v>13.550000000000001</v>
+        <v>13.55</v>
       </c>
       <c r="AE56" s="1">
-        <v>25.800000000000001</v>
+        <v>25.8</v>
       </c>
       <c r="AF56" s="1">
         <v>20</v>
       </c>
       <c r="AG56" s="1">
-        <v>5.7999999999999998</v>
+        <v>5.8</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -7263,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" ht="15">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7367,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="1">
-        <v>0.0076575999999999997</v>
+        <v>7.6575999999999997E-3</v>
       </c>
       <c r="AJ57" s="1">
         <v>0</v>
@@ -7384,6 +7299,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/ro_workstation/data/mis/archive/20260331.xlsx
+++ b/ro_workstation/data/mis/archive/20260331.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,26 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A5B32D-B857-46B1-87BB-E031DACAA453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -161,7 +152,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,8 +161,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
+      <color theme="1" tint="0.0499899983406067"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -201,37 +198,130 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -505,16 +595,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="19" max="19" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.8571428571429" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7142857142857" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="15">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -689,7 +779,7 @@
         <v>19.063429366000005</v>
       </c>
       <c r="S2" s="4">
-        <v>6.1958381999999992E-2</v>
+        <v>0.061958381999999992</v>
       </c>
       <c r="T2" s="4">
         <v>45.643704320000012</v>
@@ -752,7 +842,7 @@
         <v>2.9941510000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -844,13 +934,13 @@
         <v>22.27</v>
       </c>
       <c r="AE3" s="1">
-        <v>77.77</v>
+        <v>77.769999999999996</v>
       </c>
       <c r="AF3" s="1">
         <v>87</v>
       </c>
       <c r="AG3" s="1">
-        <v>-9.23</v>
+        <v>-9.2300000000000004</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -871,7 +961,7 @@
         <v>8.3221000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="15">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -960,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="AD4" s="1">
-        <v>21.2</v>
+        <v>21.199999999999999</v>
       </c>
       <c r="AE4" s="1">
-        <v>37.97</v>
+        <v>37.969999999999999</v>
       </c>
       <c r="AF4" s="1">
         <v>35</v>
       </c>
       <c r="AG4" s="1">
-        <v>2.97</v>
+        <v>2.9700000000000002</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -990,7 +1080,7 @@
         <v>0.10975</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="15">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1079,16 +1169,16 @@
         <v>0</v>
       </c>
       <c r="AD5" s="1">
-        <v>39.58</v>
+        <v>39.579999999999998</v>
       </c>
       <c r="AE5" s="1">
-        <v>70.92</v>
+        <v>70.920000000000002</v>
       </c>
       <c r="AF5" s="1">
         <v>45</v>
       </c>
       <c r="AG5" s="1">
-        <v>25.92</v>
+        <v>25.920000000000002</v>
       </c>
       <c r="AH5" s="1">
         <v>0</v>
@@ -1109,7 +1199,7 @@
         <v>7.1046199999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="15">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1189,7 +1279,7 @@
         <v>8633.9201909999992</v>
       </c>
       <c r="AA6" s="1">
-        <v>61.64</v>
+        <v>61.640000000000001</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -1198,16 +1288,16 @@
         <v>0</v>
       </c>
       <c r="AD6" s="1">
-        <v>26.3</v>
+        <v>26.300000000000001</v>
       </c>
       <c r="AE6" s="1">
-        <v>87.94</v>
+        <v>87.939999999999998</v>
       </c>
       <c r="AF6" s="1">
         <v>50</v>
       </c>
       <c r="AG6" s="1">
-        <v>37.94</v>
+        <v>37.939999999999998</v>
       </c>
       <c r="AH6" s="1">
         <v>0</v>
@@ -1228,7 +1318,7 @@
         <v>14.533099999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="15">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1308,7 +1398,7 @@
         <v>6366.8882773999994</v>
       </c>
       <c r="AA7" s="1">
-        <v>24.53</v>
+        <v>24.530000000000001</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
@@ -1320,13 +1410,13 @@
         <v>8.5</v>
       </c>
       <c r="AE7" s="1">
-        <v>33.03</v>
+        <v>33.030000000000001</v>
       </c>
       <c r="AF7" s="1">
         <v>45</v>
       </c>
       <c r="AG7" s="1">
-        <v>-11.97</v>
+        <v>-11.970000000000001</v>
       </c>
       <c r="AH7" s="1">
         <v>0</v>
@@ -1341,13 +1431,13 @@
         <v>0.44341999999999998</v>
       </c>
       <c r="AL7" s="1">
-        <v>4.0299999999999997E-3</v>
+        <v>0.0040299999999999997</v>
       </c>
       <c r="AM7" s="1">
         <v>5.0019</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1436,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="1">
-        <v>11.37</v>
+        <v>11.369999999999999</v>
       </c>
       <c r="AE8" s="1">
         <v>30.43</v>
@@ -1445,7 +1535,7 @@
         <v>35</v>
       </c>
       <c r="AG8" s="1">
-        <v>-4.57</v>
+        <v>-4.5700000000000003</v>
       </c>
       <c r="AH8" s="1">
         <v>0</v>
@@ -1457,16 +1547,16 @@
         <v>0.91003000000000001</v>
       </c>
       <c r="AK8" s="1">
-        <v>3.0040000000000001E-2</v>
+        <v>0.030040000000000001</v>
       </c>
       <c r="AL8" s="1">
-        <v>7.0790000000000006E-2</v>
+        <v>0.070790000000000006</v>
       </c>
       <c r="AM8" s="1">
         <v>0.88414999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="15">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1558,13 +1648,13 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="AE9" s="1">
-        <v>43.17</v>
+        <v>43.170000000000002</v>
       </c>
       <c r="AF9" s="1">
         <v>40</v>
       </c>
       <c r="AG9" s="1">
-        <v>3.17</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="AH9" s="1">
         <v>0</v>
@@ -1585,7 +1675,7 @@
         <v>2.7176</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="15">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1665,16 +1755,16 @@
         <v>15346.537002700001</v>
       </c>
       <c r="AA10" s="1">
-        <v>28.42</v>
+        <v>28.420000000000002</v>
       </c>
       <c r="AB10" s="1">
-        <v>7.61</v>
+        <v>7.6100000000000003</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>40.54</v>
+        <v>40.539999999999999</v>
       </c>
       <c r="AE10" s="1">
         <v>76.569999999999993</v>
@@ -1683,7 +1773,7 @@
         <v>80</v>
       </c>
       <c r="AG10" s="1">
-        <v>-3.43</v>
+        <v>-3.4300000000000002</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1704,7 +1794,7 @@
         <v>180.05985000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="15">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1784,7 +1874,7 @@
         <v>10071.054588200001</v>
       </c>
       <c r="AA11" s="1">
-        <v>27.15</v>
+        <v>27.149999999999999</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1796,7 +1886,7 @@
         <v>28.18</v>
       </c>
       <c r="AE11" s="1">
-        <v>55.33</v>
+        <v>55.329999999999998</v>
       </c>
       <c r="AF11" s="1">
         <v>70</v>
@@ -1823,7 +1913,7 @@
         <v>7.3209200000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="15">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1903,7 +1993,7 @@
         <v>7811.6613082000003</v>
       </c>
       <c r="AA12" s="1">
-        <v>37.58</v>
+        <v>37.579999999999998</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
@@ -1912,16 +2002,16 @@
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>13.96</v>
+        <v>13.960000000000001</v>
       </c>
       <c r="AE12" s="1">
-        <v>51.54</v>
+        <v>51.539999999999999</v>
       </c>
       <c r="AF12" s="1">
         <v>35</v>
       </c>
       <c r="AG12" s="1">
-        <v>16.54</v>
+        <v>16.539999999999999</v>
       </c>
       <c r="AH12" s="1">
         <v>0</v>
@@ -1942,7 +2032,7 @@
         <v>0.86509999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="15">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2031,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="AD13" s="1">
-        <v>22.65</v>
+        <v>22.649999999999999</v>
       </c>
       <c r="AE13" s="1">
-        <v>62.42</v>
+        <v>62.420000000000002</v>
       </c>
       <c r="AF13" s="1">
         <v>30</v>
       </c>
       <c r="AG13" s="1">
-        <v>32.42</v>
+        <v>32.420000000000002</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2055,13 +2145,13 @@
         <v>6.7509399999999999</v>
       </c>
       <c r="AL13" s="1">
-        <v>1.41E-3</v>
+        <v>0.00141</v>
       </c>
       <c r="AM13" s="1">
-        <v>9.3999999999999997E-4</v>
+        <v>0.00093999999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="15">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2168,19 +2258,19 @@
         <v>152.72031430000001</v>
       </c>
       <c r="AJ14" s="1">
-        <v>3.789E-2</v>
+        <v>0.03789</v>
       </c>
       <c r="AK14" s="1">
-        <v>4.8999999999999998E-4</v>
+        <v>0.00048999999999999998</v>
       </c>
       <c r="AL14" s="1">
         <v>6.8592899999999997</v>
       </c>
       <c r="AM14" s="1">
-        <v>9.3999999999999997E-4</v>
+        <v>0.00093999999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="15">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2260,7 +2350,7 @@
         <v>5627.4598616000003</v>
       </c>
       <c r="AA15" s="1">
-        <v>42.73</v>
+        <v>42.729999999999997</v>
       </c>
       <c r="AB15" s="1">
         <v>0</v>
@@ -2269,16 +2359,16 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1">
-        <v>6.48</v>
+        <v>6.4800000000000004</v>
       </c>
       <c r="AE15" s="1">
-        <v>49.21</v>
+        <v>49.210000000000001</v>
       </c>
       <c r="AF15" s="1">
         <v>30</v>
       </c>
       <c r="AG15" s="1">
-        <v>19.21</v>
+        <v>19.210000000000001</v>
       </c>
       <c r="AH15" s="1">
         <v>400</v>
@@ -2299,7 +2389,7 @@
         <v>2.5365700000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2379,7 +2469,7 @@
         <v>12165.066160599999</v>
       </c>
       <c r="AA16" s="1">
-        <v>49.36</v>
+        <v>49.359999999999999</v>
       </c>
       <c r="AB16" s="1">
         <v>0</v>
@@ -2388,16 +2478,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="1">
-        <v>6.28</v>
+        <v>6.2800000000000002</v>
       </c>
       <c r="AE16" s="1">
-        <v>55.64</v>
+        <v>55.640000000000001</v>
       </c>
       <c r="AF16" s="1">
         <v>33</v>
       </c>
       <c r="AG16" s="1">
-        <v>22.64</v>
+        <v>22.640000000000001</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -2418,7 +2508,7 @@
         <v>0.65498999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2510,7 +2600,7 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="AE17" s="1">
-        <v>45.12</v>
+        <v>45.119999999999997</v>
       </c>
       <c r="AF17" s="1">
         <v>35</v>
@@ -2537,7 +2627,7 @@
         <v>1.1933400000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2653,10 +2743,10 @@
         <v>2.5019100000000001</v>
       </c>
       <c r="AM18" s="1">
-        <v>1.9300000000000001E-3</v>
+        <v>0.0019300000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2754,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="AG19" s="1">
-        <v>-22.46</v>
+        <v>-22.460000000000001</v>
       </c>
       <c r="AH19" s="1">
         <v>0</v>
@@ -2775,7 +2865,7 @@
         <v>1.1154500000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2855,7 +2945,7 @@
         <v>7061.8403475999994</v>
       </c>
       <c r="AA20" s="1">
-        <v>45.89</v>
+        <v>45.890000000000001</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2864,10 +2954,10 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>10.45</v>
+        <v>10.449999999999999</v>
       </c>
       <c r="AE20" s="1">
-        <v>56.34</v>
+        <v>56.340000000000003</v>
       </c>
       <c r="AF20" s="1">
         <v>30</v>
@@ -2894,7 +2984,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2986,13 +3076,13 @@
         <v>13.6</v>
       </c>
       <c r="AE21" s="1">
-        <v>26.83</v>
+        <v>26.829999999999998</v>
       </c>
       <c r="AF21" s="1">
         <v>30</v>
       </c>
       <c r="AG21" s="1">
-        <v>-3.17</v>
+        <v>-3.1699999999999999</v>
       </c>
       <c r="AH21" s="1">
         <v>0</v>
@@ -3007,13 +3097,13 @@
         <v>0.33148</v>
       </c>
       <c r="AL21" s="1">
-        <v>6.6379999999999995E-2</v>
+        <v>0.066379999999999995</v>
       </c>
       <c r="AM21" s="1">
-        <v>2.8320000000000001E-2</v>
+        <v>0.028320000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3093,7 +3183,7 @@
         <v>5578.4743435999999</v>
       </c>
       <c r="AA22" s="1">
-        <v>48.89</v>
+        <v>48.890000000000001</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3102,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>35.86</v>
+        <v>35.859999999999999</v>
       </c>
       <c r="AE22" s="1">
         <v>84.75</v>
@@ -3120,7 +3210,7 @@
         <v>214.1566564</v>
       </c>
       <c r="AJ22" s="1">
-        <v>2.7089999999999999E-2</v>
+        <v>0.027089999999999999</v>
       </c>
       <c r="AK22" s="1">
         <v>0.39182</v>
@@ -3132,7 +3222,7 @@
         <v>0.28193000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3221,10 +3311,10 @@
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>82.24</v>
+        <v>82.239999999999995</v>
       </c>
       <c r="AE23" s="1">
-        <v>141.46</v>
+        <v>141.46000000000001</v>
       </c>
       <c r="AF23" s="1">
         <v>70</v>
@@ -3251,7 +3341,7 @@
         <v>4.7040499999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3331,7 +3421,7 @@
         <v>5025.3509590999993</v>
       </c>
       <c r="AA24" s="1">
-        <v>21.08</v>
+        <v>21.079999999999998</v>
       </c>
       <c r="AB24" s="1">
         <v>12.25</v>
@@ -3343,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="AE24" s="1">
-        <v>33.33</v>
+        <v>33.329999999999998</v>
       </c>
       <c r="AF24" s="1">
         <v>45</v>
@@ -3370,7 +3460,7 @@
         <v>11.32147</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3450,7 +3540,7 @@
         <v>3234.8239198000001</v>
       </c>
       <c r="AA25" s="1">
-        <v>21.38</v>
+        <v>21.379999999999999</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -3468,7 +3558,7 @@
         <v>25</v>
       </c>
       <c r="AG25" s="1">
-        <v>6.57</v>
+        <v>6.5700000000000003</v>
       </c>
       <c r="AH25" s="1">
         <v>0</v>
@@ -3489,7 +3579,7 @@
         <v>0.49512</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3581,13 +3671,13 @@
         <v>11.9</v>
       </c>
       <c r="AE26" s="1">
-        <v>23.89</v>
+        <v>23.890000000000001</v>
       </c>
       <c r="AF26" s="1">
         <v>32</v>
       </c>
       <c r="AG26" s="1">
-        <v>-8.11</v>
+        <v>-8.1099999999999994</v>
       </c>
       <c r="AH26" s="1">
         <v>0</v>
@@ -3599,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="1">
-        <v>0.9</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="AL26" s="1">
         <v>1.96305</v>
@@ -3608,7 +3698,7 @@
         <v>3.6840700000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3688,7 +3778,7 @@
         <v>7851.2096683999998</v>
       </c>
       <c r="AA27" s="1">
-        <v>41.16</v>
+        <v>41.159999999999997</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -3700,13 +3790,13 @@
         <v>38.450000000000003</v>
       </c>
       <c r="AE27" s="1">
-        <v>79.61</v>
+        <v>79.609999999999999</v>
       </c>
       <c r="AF27" s="1">
         <v>36</v>
       </c>
       <c r="AG27" s="1">
-        <v>43.61</v>
+        <v>43.609999999999999</v>
       </c>
       <c r="AH27" s="1">
         <v>0</v>
@@ -3727,7 +3817,7 @@
         <v>7.5196399999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3816,16 +3906,16 @@
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>2.69</v>
+        <v>2.6899999999999999</v>
       </c>
       <c r="AE28" s="1">
-        <v>22.94</v>
+        <v>22.940000000000001</v>
       </c>
       <c r="AF28" s="1">
         <v>30</v>
       </c>
       <c r="AG28" s="1">
-        <v>-7.06</v>
+        <v>-7.0599999999999996</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -3846,7 +3936,7 @@
         <v>5.9265600000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3935,16 +4025,16 @@
         <v>0</v>
       </c>
       <c r="AD29" s="1">
-        <v>8.41</v>
+        <v>8.4100000000000001</v>
       </c>
       <c r="AE29" s="1">
-        <v>45.3</v>
+        <v>45.299999999999997</v>
       </c>
       <c r="AF29" s="1">
         <v>40</v>
       </c>
       <c r="AG29" s="1">
-        <v>5.3</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="AH29" s="1">
         <v>0</v>
@@ -3953,7 +4043,7 @@
         <v>343.86590719999998</v>
       </c>
       <c r="AJ29" s="1">
-        <v>5.4760000000000003E-2</v>
+        <v>0.054760000000000003</v>
       </c>
       <c r="AK29" s="1">
         <v>1.2500199999999999</v>
@@ -3965,7 +4055,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4045,10 +4135,10 @@
         <v>9296.3004184000001</v>
       </c>
       <c r="AA30" s="1">
-        <v>25.44</v>
+        <v>25.440000000000001</v>
       </c>
       <c r="AB30" s="1">
-        <v>11.03</v>
+        <v>11.029999999999999</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
@@ -4057,13 +4147,13 @@
         <v>0</v>
       </c>
       <c r="AE30" s="1">
-        <v>36.47</v>
+        <v>36.469999999999999</v>
       </c>
       <c r="AF30" s="1">
         <v>40</v>
       </c>
       <c r="AG30" s="1">
-        <v>-3.53</v>
+        <v>-3.5299999999999998</v>
       </c>
       <c r="AH30" s="1">
         <v>0</v>
@@ -4072,7 +4162,7 @@
         <v>376.34160070000001</v>
       </c>
       <c r="AJ30" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.0000000000000002E-05</v>
       </c>
       <c r="AK30" s="1">
         <v>3.0000200000000001</v>
@@ -4084,7 +4174,7 @@
         <v>2.7058</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4176,13 +4266,13 @@
         <v>18.68</v>
       </c>
       <c r="AE31" s="1">
-        <v>52.61</v>
+        <v>52.609999999999999</v>
       </c>
       <c r="AF31" s="1">
         <v>30</v>
       </c>
       <c r="AG31" s="1">
-        <v>22.61</v>
+        <v>22.609999999999999</v>
       </c>
       <c r="AH31" s="1">
         <v>0</v>
@@ -4203,7 +4293,7 @@
         <v>3.2392400000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4322,7 +4412,7 @@
         <v>0.96345000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4420,7 +4510,7 @@
         <v>43</v>
       </c>
       <c r="AG33" s="1">
-        <v>-1.43</v>
+        <v>-1.4299999999999999</v>
       </c>
       <c r="AH33" s="1">
         <v>0</v>
@@ -4429,19 +4519,19 @@
         <v>394.3496864</v>
       </c>
       <c r="AJ33" s="1">
-        <v>1.5399999999999999E-3</v>
+        <v>0.0015399999999999999</v>
       </c>
       <c r="AK33" s="1">
-        <v>3.0949999999999998E-2</v>
+        <v>0.030949999999999998</v>
       </c>
       <c r="AL33" s="1">
         <v>1.37096</v>
       </c>
       <c r="AM33" s="1">
-        <v>2.5000000000000001E-4</v>
+        <v>0.00025000000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4521,10 +4611,10 @@
         <v>8769.8551050000005</v>
       </c>
       <c r="AA34" s="1">
-        <v>33.61</v>
+        <v>33.609999999999999</v>
       </c>
       <c r="AB34" s="1">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -4533,13 +4623,13 @@
         <v>46.18</v>
       </c>
       <c r="AE34" s="1">
-        <v>88.86</v>
+        <v>88.859999999999999</v>
       </c>
       <c r="AF34" s="1">
         <v>55</v>
       </c>
       <c r="AG34" s="1">
-        <v>33.86</v>
+        <v>33.859999999999999</v>
       </c>
       <c r="AH34" s="1">
         <v>0</v>
@@ -4557,10 +4647,10 @@
         <v>1.8021799999999999</v>
       </c>
       <c r="AM34" s="1">
-        <v>1.4E-3</v>
+        <v>0.0014</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4613,7 +4703,7 @@
         <v>291.77402190000004</v>
       </c>
       <c r="R35" s="3">
-        <v>3.1</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="S35" s="3">
         <v>0.91666669999999995</v>
@@ -4640,7 +4730,7 @@
         <v>7022.7325234999998</v>
       </c>
       <c r="AA35" s="1">
-        <v>6.58</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -4679,7 +4769,7 @@
         <v>1.05585</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4771,13 +4861,13 @@
         <v>15.6</v>
       </c>
       <c r="AE36" s="1">
-        <v>52.05</v>
+        <v>52.049999999999997</v>
       </c>
       <c r="AF36" s="1">
         <v>33</v>
       </c>
       <c r="AG36" s="1">
-        <v>19.05</v>
+        <v>19.050000000000001</v>
       </c>
       <c r="AH36" s="1">
         <v>0</v>
@@ -4795,10 +4885,10 @@
         <v>3.8515600000000001</v>
       </c>
       <c r="AM36" s="1">
-        <v>5.9749999999999998E-2</v>
+        <v>0.059749999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4878,7 +4968,7 @@
         <v>10764.5485646</v>
       </c>
       <c r="AA37" s="1">
-        <v>20.21</v>
+        <v>20.210000000000001</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
@@ -4890,13 +4980,13 @@
         <v>11.94</v>
       </c>
       <c r="AE37" s="1">
-        <v>32.15</v>
+        <v>32.149999999999999</v>
       </c>
       <c r="AF37" s="1">
         <v>34</v>
       </c>
       <c r="AG37" s="1">
-        <v>-1.85</v>
+        <v>-1.8500000000000001</v>
       </c>
       <c r="AH37" s="1">
         <v>0</v>
@@ -4905,19 +4995,19 @@
         <v>390.33103770000002</v>
       </c>
       <c r="AJ37" s="1">
-        <v>6.0630000000000003E-2</v>
+        <v>0.060630000000000003</v>
       </c>
       <c r="AK37" s="1">
         <v>0.15558</v>
       </c>
       <c r="AL37" s="1">
-        <v>7.5550000000000006E-2</v>
+        <v>0.075550000000000006</v>
       </c>
       <c r="AM37" s="1">
-        <v>2.2720000000000001E-2</v>
+        <v>0.022720000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4997,7 +5087,7 @@
         <v>7153.1224789000007</v>
       </c>
       <c r="AA38" s="1">
-        <v>22.15</v>
+        <v>22.149999999999999</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
@@ -5006,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="AD38" s="1">
-        <v>32.44</v>
+        <v>32.439999999999998</v>
       </c>
       <c r="AE38" s="1">
-        <v>54.59</v>
+        <v>54.590000000000003</v>
       </c>
       <c r="AF38" s="1">
         <v>34</v>
@@ -5024,7 +5114,7 @@
         <v>287.5915038</v>
       </c>
       <c r="AJ38" s="1">
-        <v>1.3440000000000001E-2</v>
+        <v>0.013440000000000001</v>
       </c>
       <c r="AK38" s="1">
         <v>23.326619999999998</v>
@@ -5033,10 +5123,10 @@
         <v>15.10314</v>
       </c>
       <c r="AM38" s="1">
-        <v>2.97E-3</v>
+        <v>0.00297</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5116,7 +5206,7 @@
         <v>12579.2313041</v>
       </c>
       <c r="AA39" s="1">
-        <v>22.65</v>
+        <v>22.649999999999999</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -5125,16 +5215,16 @@
         <v>0</v>
       </c>
       <c r="AD39" s="1">
-        <v>44.3</v>
+        <v>44.299999999999997</v>
       </c>
       <c r="AE39" s="1">
-        <v>66.95</v>
+        <v>66.950000000000003</v>
       </c>
       <c r="AF39" s="1">
         <v>38</v>
       </c>
       <c r="AG39" s="1">
-        <v>28.95</v>
+        <v>28.949999999999999</v>
       </c>
       <c r="AH39" s="1">
         <v>0</v>
@@ -5143,19 +5233,19 @@
         <v>544.11298729999999</v>
       </c>
       <c r="AJ39" s="1">
-        <v>3.8000000000000002E-4</v>
+        <v>0.00038000000000000002</v>
       </c>
       <c r="AK39" s="1">
-        <v>3.5040000000000002E-2</v>
+        <v>0.035040000000000002</v>
       </c>
       <c r="AL39" s="1">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096000000000000002</v>
       </c>
       <c r="AM39" s="1">
-        <v>4.2009999999999999E-2</v>
+        <v>0.042009999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5208,7 +5298,7 @@
         <v>35.648727299999997</v>
       </c>
       <c r="R40" s="3">
-        <v>0.32</v>
+        <v>0.32000000000000001</v>
       </c>
       <c r="S40" s="3">
         <v>0</v>
@@ -5235,7 +5325,7 @@
         <v>8719.3167412999992</v>
       </c>
       <c r="AA40" s="1">
-        <v>25.44</v>
+        <v>25.440000000000001</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -5247,7 +5337,7 @@
         <v>20.41</v>
       </c>
       <c r="AE40" s="1">
-        <v>45.85</v>
+        <v>45.850000000000001</v>
       </c>
       <c r="AF40" s="1">
         <v>35</v>
@@ -5274,7 +5364,7 @@
         <v>1.44652</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5354,7 +5444,7 @@
         <v>4635.5096014999999</v>
       </c>
       <c r="AA41" s="1">
-        <v>44.84</v>
+        <v>44.840000000000003</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
@@ -5363,16 +5453,16 @@
         <v>0</v>
       </c>
       <c r="AD41" s="1">
-        <v>13.03</v>
+        <v>13.029999999999999</v>
       </c>
       <c r="AE41" s="1">
-        <v>57.87</v>
+        <v>57.869999999999997</v>
       </c>
       <c r="AF41" s="1">
         <v>33</v>
       </c>
       <c r="AG41" s="1">
-        <v>24.87</v>
+        <v>24.870000000000001</v>
       </c>
       <c r="AH41" s="1">
         <v>0</v>
@@ -5384,7 +5474,7 @@
         <v>23.397929999999999</v>
       </c>
       <c r="AK41" s="1">
-        <v>3.2009999999999997E-2</v>
+        <v>0.032009999999999997</v>
       </c>
       <c r="AL41" s="1">
         <v>0.72116999999999998</v>
@@ -5393,7 +5483,7 @@
         <v>4.1247999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5485,13 +5575,13 @@
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>82.22</v>
+        <v>82.219999999999999</v>
       </c>
       <c r="AF42" s="1">
         <v>34</v>
       </c>
       <c r="AG42" s="1">
-        <v>48.22</v>
+        <v>48.219999999999999</v>
       </c>
       <c r="AH42" s="1">
         <v>0</v>
@@ -5503,16 +5593,16 @@
         <v>0.10518</v>
       </c>
       <c r="AK42" s="1">
-        <v>4.0000000000000003E-5</v>
+        <v>4.0000000000000003E-05</v>
       </c>
       <c r="AL42" s="1">
-        <v>2.0389999999999998E-2</v>
+        <v>0.020389999999999998</v>
       </c>
       <c r="AM42" s="1">
         <v>0.27528000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5592,7 +5682,7 @@
         <v>11115.6827514</v>
       </c>
       <c r="AA43" s="1">
-        <v>141.4</v>
+        <v>141.40000000000001</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
@@ -5604,13 +5694,13 @@
         <v>15.84</v>
       </c>
       <c r="AE43" s="1">
-        <v>157.24</v>
+        <v>157.24000000000001</v>
       </c>
       <c r="AF43" s="1">
         <v>30</v>
       </c>
       <c r="AG43" s="1">
-        <v>127.24</v>
+        <v>127.23999999999999</v>
       </c>
       <c r="AH43" s="1">
         <v>0</v>
@@ -5619,19 +5709,19 @@
         <v>379.05141070000002</v>
       </c>
       <c r="AJ43" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
       <c r="AK43" s="1">
-        <v>3.0000000000000001E-5</v>
+        <v>3.0000000000000001E-05</v>
       </c>
       <c r="AL43" s="1">
         <v>0</v>
       </c>
       <c r="AM43" s="1">
-        <v>1.9859999999999999E-2</v>
+        <v>0.019859999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5711,7 +5801,7 @@
         <v>4393.3398811000006</v>
       </c>
       <c r="AA44" s="1">
-        <v>24.36</v>
+        <v>24.359999999999999</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
@@ -5720,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="1">
-        <v>5.98</v>
+        <v>5.9800000000000004</v>
       </c>
       <c r="AE44" s="1">
         <v>30.34</v>
@@ -5729,7 +5819,7 @@
         <v>25</v>
       </c>
       <c r="AG44" s="1">
-        <v>5.34</v>
+        <v>5.3399999999999999</v>
       </c>
       <c r="AH44" s="1">
         <v>0</v>
@@ -5738,19 +5828,19 @@
         <v>156.19951850000001</v>
       </c>
       <c r="AJ44" s="1">
-        <v>3.2250000000000001E-2</v>
+        <v>0.032250000000000001</v>
       </c>
       <c r="AK44" s="1">
-        <v>2.1149999999999999E-2</v>
+        <v>0.021149999999999999</v>
       </c>
       <c r="AL44" s="1">
-        <v>9.0800000000000006E-2</v>
+        <v>0.090800000000000006</v>
       </c>
       <c r="AM44" s="1">
-        <v>7.2139999999999996E-2</v>
+        <v>0.072139999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5830,7 +5920,7 @@
         <v>9673.8367088999985</v>
       </c>
       <c r="AA45" s="1">
-        <v>18.22</v>
+        <v>18.219999999999999</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
@@ -5839,16 +5929,16 @@
         <v>0</v>
       </c>
       <c r="AD45" s="1">
-        <v>39.24</v>
+        <v>39.240000000000002</v>
       </c>
       <c r="AE45" s="1">
-        <v>57.46</v>
+        <v>57.460000000000001</v>
       </c>
       <c r="AF45" s="1">
         <v>40</v>
       </c>
       <c r="AG45" s="1">
-        <v>17.46</v>
+        <v>17.460000000000001</v>
       </c>
       <c r="AH45" s="1">
         <v>0</v>
@@ -5860,16 +5950,16 @@
         <v>2.9007900000000002</v>
       </c>
       <c r="AK45" s="1">
-        <v>1.6910000000000001E-2</v>
+        <v>0.016910000000000001</v>
       </c>
       <c r="AL45" s="1">
-        <v>9.3999999999999997E-4</v>
+        <v>0.00093999999999999997</v>
       </c>
       <c r="AM45" s="1">
         <v>2.15652</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5949,7 +6039,7 @@
         <v>6092.8181897000004</v>
       </c>
       <c r="AA46" s="1">
-        <v>34.47</v>
+        <v>34.469999999999999</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
@@ -5961,7 +6051,7 @@
         <v>14.09</v>
       </c>
       <c r="AE46" s="1">
-        <v>48.56</v>
+        <v>48.560000000000002</v>
       </c>
       <c r="AF46" s="1">
         <v>33</v>
@@ -5985,10 +6075,10 @@
         <v>0</v>
       </c>
       <c r="AM46" s="1">
-        <v>0.95</v>
+        <v>0.94999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6068,7 +6158,7 @@
         <v>8477.5324937999994</v>
       </c>
       <c r="AA47" s="1">
-        <v>28.37</v>
+        <v>28.370000000000001</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
@@ -6077,16 +6167,16 @@
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <v>22.58</v>
+        <v>22.579999999999998</v>
       </c>
       <c r="AE47" s="1">
-        <v>50.95</v>
+        <v>50.950000000000003</v>
       </c>
       <c r="AF47" s="1">
         <v>35</v>
       </c>
       <c r="AG47" s="1">
-        <v>15.95</v>
+        <v>15.949999999999999</v>
       </c>
       <c r="AH47" s="1">
         <v>0</v>
@@ -6098,16 +6188,16 @@
         <v>0.23404</v>
       </c>
       <c r="AK47" s="1">
-        <v>5.0029999999999998E-2</v>
+        <v>0.050029999999999998</v>
       </c>
       <c r="AL47" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.0000000000000002E-05</v>
       </c>
       <c r="AM47" s="1">
         <v>0.10032000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6160,7 +6250,7 @@
         <v>30.339821999999998</v>
       </c>
       <c r="R48" s="3">
-        <v>6.47</v>
+        <v>6.4699999999999998</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -6187,7 +6277,7 @@
         <v>7936.1799438000007</v>
       </c>
       <c r="AA48" s="1">
-        <v>27.72</v>
+        <v>27.719999999999999</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -6199,7 +6289,7 @@
         <v>16.18</v>
       </c>
       <c r="AE48" s="1">
-        <v>43.9</v>
+        <v>43.899999999999999</v>
       </c>
       <c r="AF48" s="1">
         <v>27</v>
@@ -6226,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6315,16 +6405,16 @@
         <v>0</v>
       </c>
       <c r="AD49" s="1">
-        <v>8.14</v>
+        <v>8.1400000000000006</v>
       </c>
       <c r="AE49" s="1">
-        <v>24.24</v>
+        <v>24.239999999999998</v>
       </c>
       <c r="AF49" s="1">
         <v>27</v>
       </c>
       <c r="AG49" s="1">
-        <v>-2.76</v>
+        <v>-2.7599999999999998</v>
       </c>
       <c r="AH49" s="1">
         <v>0</v>
@@ -6333,19 +6423,19 @@
         <v>170.98306170000001</v>
       </c>
       <c r="AJ49" s="1">
-        <v>1.2E-4</v>
+        <v>0.00012</v>
       </c>
       <c r="AK49" s="1">
         <v>2.11938</v>
       </c>
       <c r="AL49" s="1">
-        <v>9.0499999999999997E-2</v>
+        <v>0.090499999999999997</v>
       </c>
       <c r="AM49" s="1">
-        <v>5.1000000000000004E-4</v>
+        <v>0.00051000000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6425,7 +6515,7 @@
         <v>3151.7232076999999</v>
       </c>
       <c r="AA50" s="1">
-        <v>5.58</v>
+        <v>5.5800000000000001</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
@@ -6434,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="AD50" s="1">
-        <v>4.76</v>
+        <v>4.7599999999999998</v>
       </c>
       <c r="AE50" s="1">
         <v>10.34</v>
@@ -6443,7 +6533,7 @@
         <v>15</v>
       </c>
       <c r="AG50" s="1">
-        <v>-4.66</v>
+        <v>-4.6600000000000001</v>
       </c>
       <c r="AH50" s="1">
         <v>0</v>
@@ -6452,7 +6542,7 @@
         <v>89.4519272</v>
       </c>
       <c r="AJ50" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
       <c r="AK50" s="1">
         <v>1.70001</v>
@@ -6464,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6544,7 +6634,7 @@
         <v>4863.2046416000003</v>
       </c>
       <c r="AA51" s="1">
-        <v>42.37</v>
+        <v>42.369999999999997</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
@@ -6556,13 +6646,13 @@
         <v>10.01</v>
       </c>
       <c r="AE51" s="1">
-        <v>52.38</v>
+        <v>52.380000000000003</v>
       </c>
       <c r="AF51" s="1">
         <v>25</v>
       </c>
       <c r="AG51" s="1">
-        <v>27.38</v>
+        <v>27.379999999999999</v>
       </c>
       <c r="AH51" s="1">
         <v>0</v>
@@ -6571,10 +6661,10 @@
         <v>117.6216537</v>
       </c>
       <c r="AJ51" s="1">
-        <v>4.1880000000000001E-2</v>
+        <v>0.041880000000000001</v>
       </c>
       <c r="AK51" s="1">
-        <v>2.0119999999999999E-2</v>
+        <v>0.020119999999999999</v>
       </c>
       <c r="AL51" s="1">
         <v>0.80044000000000004</v>
@@ -6583,7 +6673,7 @@
         <v>2.0729299999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6663,7 +6753,7 @@
         <v>2933.4732304999998</v>
       </c>
       <c r="AA52" s="1">
-        <v>59.66</v>
+        <v>59.659999999999997</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -6672,16 +6762,16 @@
         <v>0</v>
       </c>
       <c r="AD52" s="1">
-        <v>31.63</v>
+        <v>31.629999999999999</v>
       </c>
       <c r="AE52" s="1">
-        <v>91.29</v>
+        <v>91.290000000000006</v>
       </c>
       <c r="AF52" s="1">
         <v>40</v>
       </c>
       <c r="AG52" s="1">
-        <v>51.29</v>
+        <v>51.289999999999999</v>
       </c>
       <c r="AH52" s="1">
         <v>0</v>
@@ -6702,7 +6792,7 @@
         <v>3.8749199999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6782,7 +6872,7 @@
         <v>6402.8617396</v>
       </c>
       <c r="AA53" s="1">
-        <v>26.89</v>
+        <v>26.890000000000001</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
@@ -6791,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <v>19.03</v>
+        <v>19.030000000000001</v>
       </c>
       <c r="AE53" s="1">
-        <v>45.92</v>
+        <v>45.920000000000002</v>
       </c>
       <c r="AF53" s="1">
         <v>28</v>
@@ -6821,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6919,7 +7009,7 @@
         <v>23</v>
       </c>
       <c r="AG54" s="1">
-        <v>-5.77</v>
+        <v>-5.7699999999999996</v>
       </c>
       <c r="AH54" s="1">
         <v>0</v>
@@ -6934,13 +7024,13 @@
         <v>0.54149999999999998</v>
       </c>
       <c r="AL54" s="1">
-        <v>6.053E-2</v>
+        <v>0.06053</v>
       </c>
       <c r="AM54" s="1">
         <v>5.2675999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7038,7 +7128,7 @@
         <v>23</v>
       </c>
       <c r="AG55" s="1">
-        <v>41.24</v>
+        <v>41.240000000000002</v>
       </c>
       <c r="AH55" s="1">
         <v>0</v>
@@ -7047,10 +7137,10 @@
         <v>181.5544897</v>
       </c>
       <c r="AJ55" s="1">
-        <v>8.1159999999999996E-2</v>
+        <v>0.081159999999999996</v>
       </c>
       <c r="AK55" s="1">
-        <v>4.8000000000000001E-4</v>
+        <v>0.00048000000000000001</v>
       </c>
       <c r="AL55" s="1">
         <v>1.15245</v>
@@ -7059,7 +7149,7 @@
         <v>2.05585</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7076,7 +7166,7 @@
         <v>919.21199319999994</v>
       </c>
       <c r="F56" s="3">
-        <v>49.52</v>
+        <v>49.520000000000003</v>
       </c>
       <c r="G56" s="3">
         <v>968.73199319999992</v>
@@ -7112,7 +7202,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="3">
-        <v>4.42</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="S56" s="3">
         <v>0</v>
@@ -7148,16 +7238,16 @@
         <v>0</v>
       </c>
       <c r="AD56" s="1">
-        <v>13.55</v>
+        <v>13.550000000000001</v>
       </c>
       <c r="AE56" s="1">
-        <v>25.8</v>
+        <v>25.800000000000001</v>
       </c>
       <c r="AF56" s="1">
         <v>20</v>
       </c>
       <c r="AG56" s="1">
-        <v>5.8</v>
+        <v>5.7999999999999998</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -7178,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7282,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="1">
-        <v>7.6575999999999997E-3</v>
+        <v>0.0076575999999999997</v>
       </c>
       <c r="AJ57" s="1">
         <v>0</v>
@@ -7299,5 +7389,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>